--- a/Churn_Modelling.xlsx
+++ b/Churn_Modelling.xlsx
@@ -2,42 +2,45 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MITS\Desktop\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59C2E6E1-2E17-486B-BCC5-D3F517A780FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B808FAB-ABB3-4642-9367-F1611686A2D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{D99E8AA3-634F-41BD-AAEB-20F67480D02F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{D99E8AA3-634F-41BD-AAEB-20F67480D02F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="11" r:id="rId1"/>
     <sheet name="Churn_Modelling" sheetId="1" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_Churn_ModellingA1N51" hidden="1">Churn_Modelling!$A$1:$N$51</definedName>
+    <definedName name="_xlcn.WorksheetConnection_Churn_ModellingA1N511" hidden="1">Churn_Modelling!$A$1:$N$51</definedName>
+    <definedName name="Slicer_Age">#N/A</definedName>
     <definedName name="Slicer_Gender">#N/A</definedName>
     <definedName name="Slicer_Geography">#N/A</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="458" r:id="rId3"/>
-    <pivotCache cacheId="461" r:id="rId4"/>
-    <pivotCache cacheId="464" r:id="rId5"/>
+    <pivotCache cacheId="495" r:id="rId3"/>
+    <pivotCache cacheId="647" r:id="rId4"/>
+    <pivotCache cacheId="650" r:id="rId5"/>
+    <pivotCache cacheId="653" r:id="rId6"/>
   </pivotCaches>
   <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{876F7934-8845-4945-9796-88D515C7AA90}">
       <x14:pivotCaches>
-        <pivotCache cacheId="416" r:id="rId6"/>
+        <pivotCache cacheId="416" r:id="rId7"/>
       </x14:pivotCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId7"/>
         <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -69,7 +72,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Churn_ModellingA1N51"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_Churn_ModellingA1N511"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -78,7 +81,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="77">
   <si>
     <t>RowNumber</t>
   </si>
@@ -297,6 +300,18 @@
   </si>
   <si>
     <t>Count of CustomerId</t>
+  </si>
+  <si>
+    <t>24-33</t>
+  </si>
+  <si>
+    <t>34-43</t>
+  </si>
+  <si>
+    <t>44-53</t>
+  </si>
+  <si>
+    <t>54-63</t>
   </si>
 </sst>
 </file>
@@ -876,470 +891,6 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Churn_Modelling.xlsx]Sheet1!PivotTable5</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
-  <c:chart>
-    <c:autoTitleDeleted val="0"/>
-    <c:pivotFmts>
-      <c:pivotFmt>
-        <c:idx val="0"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-    </c:pivotFmts>
-    <c:plotArea>
-      <c:layout/>
-      <c:barChart>
-        <c:barDir val="col"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Count of CustomerId</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$4:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Germany</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$4:$B$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>12</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-24DE-4886-BBC9-1CECB9997B03}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$3</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Sum of Exited</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$4:$A$5</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Germany</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$4:$C$5</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>4</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-24DE-4886-BBC9-1CECB9997B03}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:gapWidth val="219"/>
-        <c:overlap val="-27"/>
-        <c:axId val="905467743"/>
-        <c:axId val="905470143"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="905467743"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="905470143"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="905470143"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="905467743"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-  <c:extLst>
-    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
-      <c14:pivotOptions>
-        <c14:dropZoneFilter val="1"/>
-        <c14:dropZoneCategories val="1"/>
-        <c14:dropZoneData val="1"/>
-        <c14:dropZoneSeries val="1"/>
-        <c14:dropZonesVisible val="1"/>
-      </c14:pivotOptions>
-    </c:ext>
-    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
-      <c16:pivotOptions16>
-        <c16:showExpandCollapseFieldButtons val="1"/>
-      </c16:pivotOptions16>
-    </c:ext>
-  </c:extLst>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:pivotSource>
     <c:name>[Churn_Modelling.xlsx]Sheet1!PivotTable7</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
@@ -1556,11 +1107,26 @@
               <a:effectLst/>
             </c:spPr>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$E$4:$E$7</c:f>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1568,6 +1134,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
               </c:strCache>
@@ -1575,17 +1144,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$F$4:$F$7</c:f>
+              <c:f>Sheet1!$F$4:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>6</c:v>
+                  <c:v>23</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>24</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1656,11 +1228,26 @@
               <a:effectLst/>
             </c:spPr>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
             <c:strRef>
-              <c:f>Sheet1!$E$4:$E$7</c:f>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
               <c:strCache>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
                   <c:v>1</c:v>
                 </c:pt>
@@ -1668,6 +1255,9 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>4</c:v>
                 </c:pt>
               </c:strCache>
@@ -1675,17 +1265,20 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Sheet1!$G$4:$G$7</c:f>
+              <c:f>Sheet1!$G$4:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="3"/>
+                <c:ptCount val="4"/>
                 <c:pt idx="0">
-                  <c:v>3</c:v>
+                  <c:v>8</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1807,7 +1400,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -1820,10 +1413,6 @@
       <c:style val="2"/>
     </mc:Fallback>
   </mc:AlternateContent>
-  <c:pivotSource>
-    <c:name>[Churn_Modelling.xlsx]Sheet1!PivotTable6</c:name>
-    <c:fmtId val="0"/>
-  </c:pivotSource>
   <c:chart>
     <c:title>
       <c:overlay val="0"/>
@@ -1982,15 +1571,7 @@
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$B$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Count of CustomerId</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Count of CustomerId</c:v>
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
@@ -2167,88 +1748,411 @@
               <a:effectLst/>
             </c:spPr>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="22"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="23"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="24"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$13:$A$24</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>58</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:strLit>
+              <c:ptCount val="25"/>
+              <c:pt idx="0">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>33</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>36</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>43</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>44</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>61</c:v>
+              </c:pt>
+            </c:strLit>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$B$13:$B$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>2</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="25"/>
+              <c:pt idx="0">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>4</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>3</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>2</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2260,15 +2164,7 @@
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
-            <c:strRef>
-              <c:f>Sheet1!$C$12</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Sum of Exited</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:v>Series2</c:v>
           </c:tx>
           <c:dPt>
             <c:idx val="0"/>
@@ -2445,88 +2341,411 @@
               <a:effectLst/>
             </c:spPr>
           </c:dPt>
+          <c:dPt>
+            <c:idx val="11"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="12"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="13"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="14"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="15"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="16"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="17"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                  <a:lumOff val="20000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="18"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="19"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="20"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="21"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="22"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="23"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="80000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="24"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
           <c:cat>
-            <c:strRef>
-              <c:f>Sheet1!$A$13:$A$24</c:f>
-              <c:strCache>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>27</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>29</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>32</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>36</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>37</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>38</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>39</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>41</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>43</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>45</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>58</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
+            <c:strLit>
+              <c:ptCount val="25"/>
+              <c:pt idx="0">
+                <c:v>24</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>25</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>27</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>29</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>31</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>32</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>33</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>34</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>35</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>36</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>37</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>38</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>39</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>40</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>41</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>42</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>43</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>44</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>45</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>46</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>49</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>50</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>51</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>58</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>61</c:v>
+              </c:pt>
+            </c:strLit>
           </c:cat>
           <c:val>
-            <c:numRef>
-              <c:f>Sheet1!$C$13:$C$24</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="11"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>1</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+            <c:numLit>
+              <c:formatCode>General</c:formatCode>
+              <c:ptCount val="25"/>
+              <c:pt idx="0">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="1">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="2">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="3">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="4">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="5">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="6">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="7">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="8">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="9">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="10">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="11">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="12">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="13">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="14">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="15">
+                <c:v>2</c:v>
+              </c:pt>
+              <c:pt idx="16">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="17">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="18">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="19">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="20">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="21">
+                <c:v>0</c:v>
+              </c:pt>
+              <c:pt idx="22">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="23">
+                <c:v>1</c:v>
+              </c:pt>
+              <c:pt idx="24">
+                <c:v>0</c:v>
+              </c:pt>
+            </c:numLit>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
@@ -2545,6 +2764,1069 @@
         </c:dLbls>
         <c:firstSliceAng val="0"/>
       </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Churn_Modelling.xlsx]Sheet1!PivotTable7</c:name>
+    <c:fmtId val="17"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="1"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of CustomerId</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$F$4:$F$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>23</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-43F0-4666-9B82-8F270600A174}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Exited</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$E$4:$E$8</c:f>
+              <c:strCache>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$G$4:$G$8</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="4"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-43F0-4666-9B82-8F270600A174}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:shape val="box"/>
+        <c:axId val="787129359"/>
+        <c:axId val="787131279"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="787129359"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787131279"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="787131279"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="787129359"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Churn_Modelling.xlsx]Sheet1!PivotTable5</c:name>
+    <c:fmtId val="29"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:ln w="28575" cap="rnd">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Count of CustomerId</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Spain</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$4:$B$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>22</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>16</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7560-4487-B352-F72974DD29F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet1!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Sum of Exited</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet1!$A$4:$A$7</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>France</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Germany</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Spain</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$4:$C$7</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7560-4487-B352-F72974DD29F0}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1632536383"/>
+        <c:axId val="567646991"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1632536383"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="567646991"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="567646991"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1632536383"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2764,8 +4046,48 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2822,7 +4144,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -2873,6 +4195,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -2883,12 +4212,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2926,7 +4262,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -2969,22 +4305,23 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="dk1">
-          <a:lumMod val="65000"/>
-          <a:lumOff val="35000"/>
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
         </a:schemeClr>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
             <a:lumMod val="65000"/>
             <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:downBar>
@@ -3089,8 +4426,8 @@
       <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="75000"/>
-            <a:lumOff val="25000"/>
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
@@ -3222,19 +4559,20 @@
     <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
+      <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
       <a:solidFill>
         <a:schemeClr val="lt1"/>
       </a:solidFill>
-      <a:ln w="9525">
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
         <a:solidFill>
           <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
           </a:schemeClr>
         </a:solidFill>
+        <a:round/>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -3787,7 +5125,7 @@
 </file>
 
 <file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="286">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -3810,17 +5148,6 @@
         <a:lumOff val="35000"/>
       </a:schemeClr>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
     <cs:defRPr sz="900" kern="1200"/>
   </cs:categoryAxis>
   <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
@@ -3844,7 +5171,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
+    <cs:defRPr sz="1000" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -3895,13 +5222,6 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3912,19 +5232,12 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="25400">
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3962,7 +5275,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="0"/>
+    <cs:fillRef idx="1"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -4273,6 +5586,509 @@
           </a:schemeClr>
         </a:solidFill>
         <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
       </a:ln>
     </cs:spPr>
   </cs:upBar>
@@ -4465,52 +6281,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>185737</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>71437</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8EA12057-3F05-F5A1-4D2B-D682F1BA4DD7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>119062</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>109537</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4529,7 +6309,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4565,7 +6345,157 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Age">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55103514-B09C-E0D4-AEFE-4884C79F9467}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Age"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8858250" y="2457450"/>
+              <a:ext cx="1828800" cy="2524125"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="9" name="Chart 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DC8302B4-2ECA-1FFB-DB06-1034BF80D8EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>52387</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>409575</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="10" name="Chart 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8E71681C-1CDA-1341-8714-A6FA02123A16}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4575,13 +6505,108 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.643583217592" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7F18D322-82F0-464E-9485-C3589B2EB423}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="MITS" refreshedDate="46179.655306250002" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="50" xr:uid="{6545FB48-C602-4D04-B689-563DF0E3A8A0}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:N51" sheet="Churn_Modelling"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="RowNumber" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="50"/>
+    </cacheField>
+    <cacheField name="CustomerId" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="15568982" maxValue="15794171"/>
+    </cacheField>
+    <cacheField name="Surname" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="CreditScore" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="376" maxValue="850"/>
+    </cacheField>
+    <cacheField name="Geography" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Gender" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Age" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="24" maxValue="61" count="25">
+        <n v="42"/>
+        <n v="41"/>
+        <n v="39"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="50"/>
+        <n v="29"/>
+        <n v="27"/>
+        <n v="31"/>
+        <n v="24"/>
+        <n v="34"/>
+        <n v="25"/>
+        <n v="35"/>
+        <n v="45"/>
+        <n v="58"/>
+        <n v="32"/>
+        <n v="38"/>
+        <n v="46"/>
+        <n v="36"/>
+        <n v="33"/>
+        <n v="40"/>
+        <n v="51"/>
+        <n v="61"/>
+        <n v="49"/>
+        <n v="37"/>
+      </sharedItems>
+      <fieldGroup base="6">
+        <rangePr startNum="24" endNum="61" groupInterval="10"/>
+        <groupItems count="6">
+          <s v="&lt;24"/>
+          <s v="24-33"/>
+          <s v="34-43"/>
+          <s v="44-53"/>
+          <s v="54-63"/>
+          <s v="&gt;64"/>
+        </groupItems>
+      </fieldGroup>
+    </cacheField>
+    <cacheField name="Tenure" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="10"/>
+    </cacheField>
+    <cacheField name="Balance" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="159660.79999999999"/>
+    </cacheField>
+    <cacheField name="NumOfProducts" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4"/>
+    </cacheField>
+    <cacheField name="HasCrCard" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="IsActiveMember" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+    <cacheField name="EstimatedSalary" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="5097.67" maxValue="194365.76"/>
+    </cacheField>
+    <cacheField name="Exited" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="1"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.659553935184" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{7F18D322-82F0-464E-9485-C3589B2EB423}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="4">
     <cacheField name="[Range].[NumOfProducts].[NumOfProducts]" caption="NumOfProducts" numFmtId="0" hierarchy="9" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4" count="3">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="4" count="4">
         <n v="1"/>
         <n v="2"/>
+        <n v="3"/>
         <n v="4"/>
       </sharedItems>
       <extLst>
@@ -4589,7 +6614,8 @@
           <x15:cachedUniqueNames>
             <x15:cachedUniqueName index="0" name="[Range].[NumOfProducts].&amp;[1]"/>
             <x15:cachedUniqueName index="1" name="[Range].[NumOfProducts].&amp;[2]"/>
-            <x15:cachedUniqueName index="2" name="[Range].[NumOfProducts].&amp;[4]"/>
+            <x15:cachedUniqueName index="2" name="[Range].[NumOfProducts].&amp;[3]"/>
+            <x15:cachedUniqueName index="3" name="[Range].[NumOfProducts].&amp;[4]"/>
           </x15:cachedUniqueNames>
         </ext>
       </extLst>
@@ -4674,13 +6700,15 @@
 </pivotCacheDefinition>
 </file>
 
-<file path=xl/pivotCache/pivotCacheDefinition2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.643583564815" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FAADC83-644E-4B47-B1B7-DB8B007134C9}">
+<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.659554282407" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{8FAADC83-644E-4B47-B1B7-DB8B007134C9}">
   <cacheSource type="external" connectionId="1"/>
   <cacheFields count="3">
     <cacheField name="[Range].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems count="1">
+      <sharedItems count="3">
+        <s v="France"/>
         <s v="Germany"/>
+        <s v="Spain"/>
       </sharedItems>
     </cacheField>
     <cacheField name="[Measures].[Sum of Exited]" caption="Sum of Exited" numFmtId="0" hierarchy="17" level="32767"/>
@@ -4698,123 +6726,7 @@
       </fieldsUsage>
     </cacheHierarchy>
     <cacheHierarchy uniqueName="[Range].[Gender]" caption="Gender" attribute="1" defaultMemberUniqueName="[Range].[Gender].[All]" allUniqueName="[Range].[Gender].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Tenure]" caption="Tenure" attribute="1" defaultMemberUniqueName="[Range].[Tenure].[All]" allUniqueName="[Range].[Tenure].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Balance]" caption="Balance" attribute="1" defaultMemberUniqueName="[Range].[Balance].[All]" allUniqueName="[Range].[Balance].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[NumOfProducts]" caption="NumOfProducts" attribute="1" defaultMemberUniqueName="[Range].[NumOfProducts].[All]" allUniqueName="[Range].[NumOfProducts].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[HasCrCard]" caption="HasCrCard" attribute="1" defaultMemberUniqueName="[Range].[HasCrCard].[All]" allUniqueName="[Range].[HasCrCard].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[IsActiveMember]" caption="IsActiveMember" attribute="1" defaultMemberUniqueName="[Range].[IsActiveMember].[All]" allUniqueName="[Range].[IsActiveMember].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[EstimatedSalary]" caption="EstimatedSalary" attribute="1" defaultMemberUniqueName="[Range].[EstimatedSalary].[All]" allUniqueName="[Range].[EstimatedSalary].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Exited]" caption="Exited" attribute="1" defaultMemberUniqueName="[Range].[Exited].[All]" allUniqueName="[Range].[Exited].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Measures].[__XL_Count Range]" caption="__XL_Count Range" measure="1" displayFolder="" measureGroup="Range" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
-    <cacheHierarchy uniqueName="[Measures].[Sum of CustomerId]" caption="Sum of CustomerId" measure="1" displayFolder="" measureGroup="Range" count="0" hidden="1">
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Sum of Exited]" caption="Sum of Exited" measure="1" displayFolder="" measureGroup="Range" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="1"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="13"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Measures].[Count of CustomerId]" caption="Count of CustomerId" measure="1" displayFolder="" measureGroup="Range" count="0" oneField="1" hidden="1">
-      <fieldsUsage count="1">
-        <fieldUsage x="2"/>
-      </fieldsUsage>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
-          <x15:cacheHierarchy aggregatedColumn="1"/>
-        </ext>
-      </extLst>
-    </cacheHierarchy>
-  </cacheHierarchies>
-  <kpis count="0"/>
-  <dimensions count="2">
-    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
-    <dimension name="Range" uniqueName="[Range]" caption="Range"/>
-  </dimensions>
-  <measureGroups count="1">
-    <measureGroup name="Range" caption="Range"/>
-  </measureGroups>
-  <maps count="1">
-    <map measureGroup="0" dimension="1"/>
-  </maps>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
-      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
-    </ext>
-  </extLst>
-</pivotCacheDefinition>
-</file>
-
-<file path=xl/pivotCache/pivotCacheDefinition3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.643588078703" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{2EA9EA91-F429-4021-889C-F9170C6428E9}">
-  <cacheSource type="external" connectionId="1"/>
-  <cacheFields count="4">
-    <cacheField name="[Range].[Age].[Age]" caption="Age" numFmtId="0" hierarchy="6" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="27" maxValue="58" count="11">
-        <n v="27"/>
-        <n v="29"/>
-        <n v="32"/>
-        <n v="36"/>
-        <n v="37"/>
-        <n v="38"/>
-        <n v="39"/>
-        <n v="41"/>
-        <n v="43"/>
-        <n v="45"/>
-        <n v="58"/>
-      </sharedItems>
-      <extLst>
-        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
-          <x15:cachedUniqueNames>
-            <x15:cachedUniqueName index="0" name="[Range].[Age].&amp;[27]"/>
-            <x15:cachedUniqueName index="1" name="[Range].[Age].&amp;[29]"/>
-            <x15:cachedUniqueName index="2" name="[Range].[Age].&amp;[32]"/>
-            <x15:cachedUniqueName index="3" name="[Range].[Age].&amp;[36]"/>
-            <x15:cachedUniqueName index="4" name="[Range].[Age].&amp;[37]"/>
-            <x15:cachedUniqueName index="5" name="[Range].[Age].&amp;[38]"/>
-            <x15:cachedUniqueName index="6" name="[Range].[Age].&amp;[39]"/>
-            <x15:cachedUniqueName index="7" name="[Range].[Age].&amp;[41]"/>
-            <x15:cachedUniqueName index="8" name="[Range].[Age].&amp;[43]"/>
-            <x15:cachedUniqueName index="9" name="[Range].[Age].&amp;[45]"/>
-            <x15:cachedUniqueName index="10" name="[Range].[Age].&amp;[58]"/>
-          </x15:cachedUniqueNames>
-        </ext>
-      </extLst>
-    </cacheField>
-    <cacheField name="[Measures].[Sum of Exited]" caption="Sum of Exited" numFmtId="0" hierarchy="17" level="32767"/>
-    <cacheField name="[Measures].[Count of CustomerId]" caption="Count of CustomerId" numFmtId="0" hierarchy="18" level="32767"/>
-    <cacheField name="[Range].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="4" level="1">
-      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
-    </cacheField>
-  </cacheFields>
-  <cacheHierarchies count="19">
-    <cacheHierarchy uniqueName="[Range].[RowNumber]" caption="RowNumber" attribute="1" defaultMemberUniqueName="[Range].[RowNumber].[All]" allUniqueName="[Range].[RowNumber].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[CustomerId]" caption="CustomerId" attribute="1" defaultMemberUniqueName="[Range].[CustomerId].[All]" allUniqueName="[Range].[CustomerId].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Surname]" caption="Surname" attribute="1" defaultMemberUniqueName="[Range].[Surname].[All]" allUniqueName="[Range].[Surname].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[CreditScore]" caption="CreditScore" attribute="1" defaultMemberUniqueName="[Range].[CreditScore].[All]" allUniqueName="[Range].[CreditScore].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Range].[Geography].[All]" allUniqueName="[Range].[Geography].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="3"/>
-      </fieldsUsage>
-    </cacheHierarchy>
-    <cacheHierarchy uniqueName="[Range].[Gender]" caption="Gender" attribute="1" defaultMemberUniqueName="[Range].[Gender].[All]" allUniqueName="[Range].[Gender].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
-      <fieldsUsage count="2">
-        <fieldUsage x="-1"/>
-        <fieldUsage x="0"/>
-      </fieldsUsage>
-    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Tenure]" caption="Tenure" attribute="1" defaultMemberUniqueName="[Range].[Tenure].[All]" allUniqueName="[Range].[Tenure].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Balance]" caption="Balance" attribute="1" defaultMemberUniqueName="[Range].[Balance].[All]" allUniqueName="[Range].[Balance].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[NumOfProducts]" caption="NumOfProducts" attribute="1" defaultMemberUniqueName="[Range].[NumOfProducts].[All]" allUniqueName="[Range].[NumOfProducts].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
@@ -4872,6 +6784,150 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.65955462963" backgroundQuery="1" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{5CC9449D-DC59-4A5A-8B8F-61FF667C6464}">
+  <cacheSource type="external" connectionId="1"/>
+  <cacheFields count="4">
+    <cacheField name="[Range].[Age].[Age]" caption="Age" numFmtId="0" hierarchy="6" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="24" maxValue="61" count="25">
+        <n v="24"/>
+        <n v="25"/>
+        <n v="27"/>
+        <n v="29"/>
+        <n v="31"/>
+        <n v="32"/>
+        <n v="33"/>
+        <n v="34"/>
+        <n v="35"/>
+        <n v="36"/>
+        <n v="37"/>
+        <n v="38"/>
+        <n v="39"/>
+        <n v="40"/>
+        <n v="41"/>
+        <n v="42"/>
+        <n v="43"/>
+        <n v="44"/>
+        <n v="45"/>
+        <n v="46"/>
+        <n v="49"/>
+        <n v="50"/>
+        <n v="51"/>
+        <n v="58"/>
+        <n v="61"/>
+      </sharedItems>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{4F2E5C28-24EA-4eb8-9CBF-B6C8F9C3D259}">
+          <x15:cachedUniqueNames>
+            <x15:cachedUniqueName index="0" name="[Range].[Age].&amp;[24]"/>
+            <x15:cachedUniqueName index="1" name="[Range].[Age].&amp;[25]"/>
+            <x15:cachedUniqueName index="2" name="[Range].[Age].&amp;[27]"/>
+            <x15:cachedUniqueName index="3" name="[Range].[Age].&amp;[29]"/>
+            <x15:cachedUniqueName index="4" name="[Range].[Age].&amp;[31]"/>
+            <x15:cachedUniqueName index="5" name="[Range].[Age].&amp;[32]"/>
+            <x15:cachedUniqueName index="6" name="[Range].[Age].&amp;[33]"/>
+            <x15:cachedUniqueName index="7" name="[Range].[Age].&amp;[34]"/>
+            <x15:cachedUniqueName index="8" name="[Range].[Age].&amp;[35]"/>
+            <x15:cachedUniqueName index="9" name="[Range].[Age].&amp;[36]"/>
+            <x15:cachedUniqueName index="10" name="[Range].[Age].&amp;[37]"/>
+            <x15:cachedUniqueName index="11" name="[Range].[Age].&amp;[38]"/>
+            <x15:cachedUniqueName index="12" name="[Range].[Age].&amp;[39]"/>
+            <x15:cachedUniqueName index="13" name="[Range].[Age].&amp;[40]"/>
+            <x15:cachedUniqueName index="14" name="[Range].[Age].&amp;[41]"/>
+            <x15:cachedUniqueName index="15" name="[Range].[Age].&amp;[42]"/>
+            <x15:cachedUniqueName index="16" name="[Range].[Age].&amp;[43]"/>
+            <x15:cachedUniqueName index="17" name="[Range].[Age].&amp;[44]"/>
+            <x15:cachedUniqueName index="18" name="[Range].[Age].&amp;[45]"/>
+            <x15:cachedUniqueName index="19" name="[Range].[Age].&amp;[46]"/>
+            <x15:cachedUniqueName index="20" name="[Range].[Age].&amp;[49]"/>
+            <x15:cachedUniqueName index="21" name="[Range].[Age].&amp;[50]"/>
+            <x15:cachedUniqueName index="22" name="[Range].[Age].&amp;[51]"/>
+            <x15:cachedUniqueName index="23" name="[Range].[Age].&amp;[58]"/>
+            <x15:cachedUniqueName index="24" name="[Range].[Age].&amp;[61]"/>
+          </x15:cachedUniqueNames>
+        </ext>
+      </extLst>
+    </cacheField>
+    <cacheField name="[Measures].[Count of CustomerId]" caption="Count of CustomerId" numFmtId="0" hierarchy="18" level="32767"/>
+    <cacheField name="[Measures].[Sum of Exited]" caption="Sum of Exited" numFmtId="0" hierarchy="17" level="32767"/>
+    <cacheField name="[Range].[Geography].[Geography]" caption="Geography" numFmtId="0" hierarchy="4" level="1">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsString="0"/>
+    </cacheField>
+  </cacheFields>
+  <cacheHierarchies count="19">
+    <cacheHierarchy uniqueName="[Range].[RowNumber]" caption="RowNumber" attribute="1" defaultMemberUniqueName="[Range].[RowNumber].[All]" allUniqueName="[Range].[RowNumber].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[CustomerId]" caption="CustomerId" attribute="1" defaultMemberUniqueName="[Range].[CustomerId].[All]" allUniqueName="[Range].[CustomerId].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Surname]" caption="Surname" attribute="1" defaultMemberUniqueName="[Range].[Surname].[All]" allUniqueName="[Range].[Surname].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[CreditScore]" caption="CreditScore" attribute="1" defaultMemberUniqueName="[Range].[CreditScore].[All]" allUniqueName="[Range].[CreditScore].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Range].[Geography].[All]" allUniqueName="[Range].[Geography].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="3"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Range].[Gender]" caption="Gender" attribute="1" defaultMemberUniqueName="[Range].[Gender].[All]" allUniqueName="[Range].[Gender].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0">
+      <fieldsUsage count="2">
+        <fieldUsage x="-1"/>
+        <fieldUsage x="0"/>
+      </fieldsUsage>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Range].[Tenure]" caption="Tenure" attribute="1" defaultMemberUniqueName="[Range].[Tenure].[All]" allUniqueName="[Range].[Tenure].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Balance]" caption="Balance" attribute="1" defaultMemberUniqueName="[Range].[Balance].[All]" allUniqueName="[Range].[Balance].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[NumOfProducts]" caption="NumOfProducts" attribute="1" defaultMemberUniqueName="[Range].[NumOfProducts].[All]" allUniqueName="[Range].[NumOfProducts].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[HasCrCard]" caption="HasCrCard" attribute="1" defaultMemberUniqueName="[Range].[HasCrCard].[All]" allUniqueName="[Range].[HasCrCard].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[IsActiveMember]" caption="IsActiveMember" attribute="1" defaultMemberUniqueName="[Range].[IsActiveMember].[All]" allUniqueName="[Range].[IsActiveMember].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[EstimatedSalary]" caption="EstimatedSalary" attribute="1" defaultMemberUniqueName="[Range].[EstimatedSalary].[All]" allUniqueName="[Range].[EstimatedSalary].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Exited]" caption="Exited" attribute="1" defaultMemberUniqueName="[Range].[Exited].[All]" allUniqueName="[Range].[Exited].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Measures].[__XL_Count Range]" caption="__XL_Count Range" measure="1" displayFolder="" measureGroup="Range" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[__No measures defined]" caption="__No measures defined" measure="1" displayFolder="" count="0" hidden="1"/>
+    <cacheHierarchy uniqueName="[Measures].[Sum of CustomerId]" caption="Sum of CustomerId" measure="1" displayFolder="" measureGroup="Range" count="0" hidden="1">
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Sum of Exited]" caption="Sum of Exited" measure="1" displayFolder="" measureGroup="Range" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="2"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="13"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+    <cacheHierarchy uniqueName="[Measures].[Count of CustomerId]" caption="Count of CustomerId" measure="1" displayFolder="" measureGroup="Range" count="0" oneField="1" hidden="1">
+      <fieldsUsage count="1">
+        <fieldUsage x="1"/>
+      </fieldsUsage>
+      <extLst>
+        <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{B97F6D7D-B522-45F9-BDA1-12C45D357490}">
+          <x15:cacheHierarchy aggregatedColumn="1"/>
+        </ext>
+      </extLst>
+    </cacheHierarchy>
+  </cacheHierarchies>
+  <kpis count="0"/>
+  <dimensions count="2">
+    <dimension measure="1" name="Measures" uniqueName="[Measures]" caption="Measures"/>
+    <dimension name="Range" uniqueName="[Range]" caption="Range"/>
+  </dimensions>
+  <measureGroups count="1">
+    <measureGroup name="Range" caption="Range"/>
+  </measureGroups>
+  <maps count="1">
+    <map measureGroup="0" dimension="1"/>
+  </maps>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition supportSubqueryNonVisual="1" supportSubqueryCalcMem="1" supportAddCalcMems="1"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition5.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" saveData="0" refreshedBy="MITS" refreshedDate="46179.63880763889" backgroundQuery="1" createdVersion="3" refreshedVersion="8" minRefreshableVersion="3" recordCount="0" supportSubquery="1" supportAdvancedDrill="1" xr:uid="{A470DABE-CF3B-4657-BC3B-6944DEBE4A6B}">
   <cacheSource type="external" connectionId="1">
     <extLst>
@@ -4888,7 +6944,7 @@
     <cacheHierarchy uniqueName="[Range].[CreditScore]" caption="CreditScore" attribute="1" defaultMemberUniqueName="[Range].[CreditScore].[All]" allUniqueName="[Range].[CreditScore].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Geography]" caption="Geography" attribute="1" defaultMemberUniqueName="[Range].[Geography].[All]" allUniqueName="[Range].[Geography].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Gender]" caption="Gender" attribute="1" defaultMemberUniqueName="[Range].[Gender].[All]" allUniqueName="[Range].[Gender].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="130" unbalanced="0"/>
-    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
+    <cacheHierarchy uniqueName="[Range].[Age]" caption="Age" attribute="1" defaultMemberUniqueName="[Range].[Age].[All]" allUniqueName="[Range].[Age].[All]" dimensionUniqueName="[Range]" displayFolder="" count="2" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Tenure]" caption="Tenure" attribute="1" defaultMemberUniqueName="[Range].[Tenure].[All]" allUniqueName="[Range].[Tenure].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[Balance]" caption="Balance" attribute="1" defaultMemberUniqueName="[Range].[Balance].[All]" allUniqueName="[Range].[Balance].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="5" unbalanced="0"/>
     <cacheHierarchy uniqueName="[Range].[NumOfProducts]" caption="NumOfProducts" attribute="1" defaultMemberUniqueName="[Range].[NumOfProducts].[All]" allUniqueName="[Range].[NumOfProducts].[All]" dimensionUniqueName="[Range]" displayFolder="" count="0" memberValueDatatype="20" unbalanced="0"/>
@@ -4929,15 +6985,842 @@
 </pivotCacheDefinition>
 </file>
 
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="50">
+  <r>
+    <n v="1"/>
+    <n v="15634602"/>
+    <s v="Hargrave"/>
+    <n v="619"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="101348.88"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <n v="15647311"/>
+    <s v="Hill"/>
+    <n v="608"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="1"/>
+    <n v="1"/>
+    <n v="83807.86"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="112542.58"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <n v="15619304"/>
+    <s v="Onio"/>
+    <n v="502"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="0"/>
+    <n v="8"/>
+    <n v="159660.79999999999"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="113931.57"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <n v="15701354"/>
+    <s v="Boni"/>
+    <n v="699"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="93826.63"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <n v="15737888"/>
+    <s v="Mitchell"/>
+    <n v="850"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="3"/>
+    <n v="2"/>
+    <n v="125510.82"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="79084.100000000006"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <n v="15574012"/>
+    <s v="Chu"/>
+    <n v="645"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <n v="8"/>
+    <n v="113755.78"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="149756.71"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <n v="15592531"/>
+    <s v="Bartlett"/>
+    <n v="822"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="5"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="10062.799999999999"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <n v="15656148"/>
+    <s v="Obinna"/>
+    <n v="376"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="6"/>
+    <n v="4"/>
+    <n v="115046.74"/>
+    <n v="4"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="119346.88"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <n v="15792365"/>
+    <s v="He"/>
+    <n v="501"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <n v="4"/>
+    <n v="142051.07"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="74940.5"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <n v="15592389"/>
+    <s v="H?"/>
+    <n v="684"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="7"/>
+    <n v="2"/>
+    <n v="134603.88"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="71725.73"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <n v="15767821"/>
+    <s v="Bearce"/>
+    <n v="528"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="8"/>
+    <n v="6"/>
+    <n v="102016.72"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="80181.119999999995"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <n v="15737173"/>
+    <s v="Andrews"/>
+    <n v="497"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="9"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="76390.009999999995"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <n v="15632264"/>
+    <s v="Kay"/>
+    <n v="476"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="10"/>
+    <n v="10"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="26260.98"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <n v="15691483"/>
+    <s v="Chin"/>
+    <n v="549"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="11"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="190857.79"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <n v="15600882"/>
+    <s v="Scott"/>
+    <n v="635"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="12"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="65951.649999999994"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <n v="15643966"/>
+    <s v="Goforth"/>
+    <n v="616"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="13"/>
+    <n v="3"/>
+    <n v="143129.41"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="64327.26"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <n v="15737452"/>
+    <s v="Romeo"/>
+    <n v="653"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="14"/>
+    <n v="1"/>
+    <n v="132602.88"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="5097.67"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <n v="15788218"/>
+    <s v="Henderson"/>
+    <n v="549"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="9"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="14406.41"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <n v="15661507"/>
+    <s v="Muldrow"/>
+    <n v="587"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="13"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="158684.81"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <n v="15568982"/>
+    <s v="Hao"/>
+    <n v="726"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="9"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="54724.03"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="21"/>
+    <n v="15577657"/>
+    <s v="McDonald"/>
+    <n v="732"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="170886.17"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="22"/>
+    <n v="15597945"/>
+    <s v="Dellucci"/>
+    <n v="636"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="15"/>
+    <n v="8"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="138555.46"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="23"/>
+    <n v="15699309"/>
+    <s v="Gerasimov"/>
+    <n v="510"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="16"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="118913.53"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="24"/>
+    <n v="15725737"/>
+    <s v="Mosman"/>
+    <n v="669"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="17"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="8487.75"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="25"/>
+    <n v="15625047"/>
+    <s v="Yen"/>
+    <n v="846"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="16"/>
+    <n v="5"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="187616.16"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="26"/>
+    <n v="15738191"/>
+    <s v="Maclean"/>
+    <n v="577"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="11"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="124508.29"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="27"/>
+    <n v="15736816"/>
+    <s v="Young"/>
+    <n v="756"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="18"/>
+    <n v="2"/>
+    <n v="136815.64000000001"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="170041.95"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="28"/>
+    <n v="15700772"/>
+    <s v="Nebechi"/>
+    <n v="571"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="4"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="38433.35"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="29"/>
+    <n v="15728693"/>
+    <s v="McWilliams"/>
+    <n v="574"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="3"/>
+    <n v="3"/>
+    <n v="141349.43"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="100187.43"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="30"/>
+    <n v="15656300"/>
+    <s v="Lucciano"/>
+    <n v="411"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="6"/>
+    <n v="0"/>
+    <n v="59697.17"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="53483.21"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="31"/>
+    <n v="15589475"/>
+    <s v="Azikiwe"/>
+    <n v="591"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <n v="3"/>
+    <n v="0"/>
+    <n v="3"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="140469.38"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="32"/>
+    <n v="15706552"/>
+    <s v="Odinakachukwu"/>
+    <n v="533"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="18"/>
+    <n v="7"/>
+    <n v="85311.7"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="156731.91"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="33"/>
+    <n v="15750181"/>
+    <s v="Sanderson"/>
+    <n v="553"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <n v="9"/>
+    <n v="110112.54"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="81898.81"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="34"/>
+    <n v="15659428"/>
+    <s v="Maggard"/>
+    <n v="520"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="0"/>
+    <n v="6"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="34410.550000000003"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="35"/>
+    <n v="15732963"/>
+    <s v="Clements"/>
+    <n v="722"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="6"/>
+    <n v="9"/>
+    <n v="0"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="142033.07"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="36"/>
+    <n v="15794171"/>
+    <s v="Lombardo"/>
+    <n v="475"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="13"/>
+    <n v="0"/>
+    <n v="134264.04"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="27822.99"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="37"/>
+    <n v="15788448"/>
+    <s v="Watson"/>
+    <n v="490"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="8"/>
+    <n v="3"/>
+    <n v="145260.23000000001"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="114066.77"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="38"/>
+    <n v="15729599"/>
+    <s v="Lorenzo"/>
+    <n v="804"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="19"/>
+    <n v="7"/>
+    <n v="76548.600000000006"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="98453.45"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="39"/>
+    <n v="15717426"/>
+    <s v="Armstrong"/>
+    <n v="850"/>
+    <s v="France"/>
+    <s v="Male"/>
+    <x v="18"/>
+    <n v="7"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="40812.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="40"/>
+    <n v="15585768"/>
+    <s v="Cameron"/>
+    <n v="582"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="1"/>
+    <n v="6"/>
+    <n v="70349.48"/>
+    <n v="2"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="178074.04"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="41"/>
+    <n v="15619360"/>
+    <s v="Hsiao"/>
+    <n v="472"/>
+    <s v="Spain"/>
+    <s v="Male"/>
+    <x v="20"/>
+    <n v="4"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="70154.22"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="42"/>
+    <n v="15738148"/>
+    <s v="Clarke"/>
+    <n v="465"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="21"/>
+    <n v="8"/>
+    <n v="122522.32"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="181297.65"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="43"/>
+    <n v="15687946"/>
+    <s v="Osborne"/>
+    <n v="556"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="22"/>
+    <n v="2"/>
+    <n v="117419.35"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="94153.83"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="44"/>
+    <n v="15755196"/>
+    <s v="Lavine"/>
+    <n v="834"/>
+    <s v="France"/>
+    <s v="Female"/>
+    <x v="23"/>
+    <n v="2"/>
+    <n v="131394.56"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="0"/>
+    <n v="194365.76"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="45"/>
+    <n v="15684171"/>
+    <s v="Bianchi"/>
+    <n v="660"/>
+    <s v="Spain"/>
+    <s v="Female"/>
+    <x v="22"/>
+    <n v="5"/>
+    <n v="155931.10999999999"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="158338.39000000001"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="46"/>
+    <n v="15754849"/>
+    <s v="Tyler"/>
+    <n v="776"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="15"/>
+    <n v="4"/>
+    <n v="109421.13"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="126517.46"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="47"/>
+    <n v="15602280"/>
+    <s v="Martin"/>
+    <n v="829"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="7"/>
+    <n v="9"/>
+    <n v="112045.67"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="119708.21"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="48"/>
+    <n v="15771573"/>
+    <s v="Okagbue"/>
+    <n v="637"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="2"/>
+    <n v="9"/>
+    <n v="137843.79999999999"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="1"/>
+    <n v="117622.8"/>
+    <n v="1"/>
+  </r>
+  <r>
+    <n v="49"/>
+    <n v="15766205"/>
+    <s v="Yin"/>
+    <n v="550"/>
+    <s v="Germany"/>
+    <s v="Male"/>
+    <x v="16"/>
+    <n v="2"/>
+    <n v="103391.38"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="1"/>
+    <n v="90878.13"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <n v="50"/>
+    <n v="15771873"/>
+    <s v="Buccho"/>
+    <n v="776"/>
+    <s v="Germany"/>
+    <s v="Female"/>
+    <x v="24"/>
+    <n v="2"/>
+    <n v="103769.22"/>
+    <n v="2"/>
+    <n v="1"/>
+    <n v="0"/>
+    <n v="194099.12"/>
+    <n v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18BA679E-F736-4EC8-BF2B-58B57CEC9C33}" name="PivotTable7" cacheId="458" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="E3:G7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FF9FC391-AEF7-452D-84E2-8C46792F7727}" name="PivotTable9" cacheId="653" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A11:C37" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
     <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="3">
+      <items count="25">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
@@ -4947,7 +7830,7 @@
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="4">
+  <rowItems count="26">
     <i>
       <x/>
     </i>
@@ -4956,6 +7839,243 @@
     </i>
     <i>
       <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i>
+      <x v="7"/>
+    </i>
+    <i>
+      <x v="8"/>
+    </i>
+    <i>
+      <x v="9"/>
+    </i>
+    <i>
+      <x v="10"/>
+    </i>
+    <i>
+      <x v="11"/>
+    </i>
+    <i>
+      <x v="12"/>
+    </i>
+    <i>
+      <x v="13"/>
+    </i>
+    <i>
+      <x v="14"/>
+    </i>
+    <i>
+      <x v="15"/>
+    </i>
+    <i>
+      <x v="16"/>
+    </i>
+    <i>
+      <x v="17"/>
+    </i>
+    <i>
+      <x v="18"/>
+    </i>
+    <i>
+      <x v="19"/>
+    </i>
+    <i>
+      <x v="20"/>
+    </i>
+    <i>
+      <x v="21"/>
+    </i>
+    <i>
+      <x v="22"/>
+    </i>
+    <i>
+      <x v="23"/>
+    </i>
+    <i>
+      <x v="24"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of CustomerId" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Exited" fld="2" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotHierarchies count="19">
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy dragToData="1" caption="Count of CustomerId"/>
+  </pivotHierarchies>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <rowHierarchiesUsage count="1">
+    <rowHierarchyUsage hierarchyUsage="6"/>
+  </rowHierarchiesUsage>
+  <colHierarchiesUsage count="1">
+    <colHierarchyUsage hierarchyUsage="-2"/>
+  </colHierarchiesUsage>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
+      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Churn_Modelling!$A$1:$N$51">
+        <x15:activeTabTopLevelEntity name="[Range]"/>
+      </x15:pivotTableUISettings>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{F0762ACB-CE78-46C7-B1D3-C4E9AA7B45D6}" name="PivotTable8" cacheId="495" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A41:C46" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="6"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Count of CustomerId" fld="1" subtotal="count" baseField="6" baseItem="0"/>
+    <dataField name="Sum of Exited" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{18BA679E-F736-4EC8-BF2B-58B57CEC9C33}" name="PivotTable7" cacheId="647" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="18">
+  <location ref="E3:G8" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="4">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
+    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -4976,7 +8096,7 @@
     <dataField name="Count of CustomerId" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Sum of Exited" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -4995,17 +8115,49 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="1" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="1" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotHierarchies count="19">
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
-      <members count="1" level="1">
-        <member name="[Range].[Geography].&amp;[Germany]"/>
-      </members>
-    </pivotHierarchy>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -5044,34 +8196,24 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8082ECD-6AE1-4DA6-A65D-8FD6FBF3DE5C}" name="PivotTable6" cacheId="464" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A12:C24" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="4">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultAttributeDrillState="1">
-      <items count="12">
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{252E5920-5AE2-4EBA-A2D2-814DA8102CD3}" name="PivotTable5" cacheId="650" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" subtotalHiddenItems="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="30">
+  <location ref="A3:C7" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="3">
+    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
+      <items count="3">
         <item x="0"/>
         <item x="1"/>
         <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item t="default"/>
       </items>
     </pivotField>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
     <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1"/>
   </pivotFields>
   <rowFields count="1">
     <field x="0"/>
   </rowFields>
-  <rowItems count="12">
+  <rowItems count="4">
     <i>
       <x/>
     </i>
@@ -5080,30 +8222,6 @@
     </i>
     <i>
       <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
     </i>
     <i t="grand">
       <x/>
@@ -5124,7 +8242,7 @@
     <dataField name="Count of CustomerId" fld="2" subtotal="count" baseField="0" baseItem="0"/>
     <dataField name="Sum of Exited" fld="1" baseField="0" baseItem="0"/>
   </dataFields>
-  <chartFormats count="2">
+  <chartFormats count="6">
     <chartFormat chart="0" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -5143,95 +8261,7 @@
         </references>
       </pivotArea>
     </chartFormat>
-  </chartFormats>
-  <pivotHierarchies count="19">
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1">
-      <members count="1" level="1">
-        <member name="[Range].[Geography].&amp;[Germany]"/>
-      </members>
-    </pivotHierarchy>
-    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToRow="0" dragToCol="0" dragToPage="0" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
-    <pivotHierarchy dragToData="1" caption="Count of CustomerId"/>
-  </pivotHierarchies>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <rowHierarchiesUsage count="1">
-    <rowHierarchyUsage hierarchyUsage="6"/>
-  </rowHierarchiesUsage>
-  <colHierarchiesUsage count="1">
-    <colHierarchyUsage hierarchyUsage="-2"/>
-  </colHierarchiesUsage>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" calculatedMembersInFilters="1" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{E67621CE-5B39-4880-91FE-76760E9C1902}">
-      <x15:pivotTableUISettings sourceDataName="WorksheetConnection_Churn_Modelling!$A$1:$N$51">
-        <x15:activeTabTopLevelEntity name="[Range]"/>
-      </x15:pivotTableUISettings>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16 EnabledSubtotalsDefault="0" SubtotalsOnTopDefault="0"/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{252E5920-5AE2-4EBA-A2D2-814DA8102CD3}" name="PivotTable5" cacheId="461" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
-  <location ref="A3:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="3">
-    <pivotField axis="axisRow" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
-      <items count="1">
-        <item s="1" x="0"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-    <pivotField dataField="1" subtotalTop="0" showAll="0" defaultSubtotal="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="0"/>
-  </rowFields>
-  <rowItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="-2"/>
-  </colFields>
-  <colItems count="2">
-    <i>
-      <x/>
-    </i>
-    <i i="1">
-      <x v="1"/>
-    </i>
-  </colItems>
-  <dataFields count="2">
-    <dataField name="Count of CustomerId" fld="2" subtotal="count" baseField="0" baseItem="0"/>
-    <dataField name="Sum of Exited" fld="1" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="2">
-    <chartFormat chart="0" format="0" series="1">
+    <chartFormat chart="1" format="2" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5240,7 +8270,25 @@
         </references>
       </pivotArea>
     </chartFormat>
-    <chartFormat chart="0" format="1" series="1">
+    <chartFormat chart="1" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="29" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="29" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -5257,7 +8305,7 @@
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
-    <pivotHierarchy dragToData="1"/>
+    <pivotHierarchy multipleItemSelectionAllowed="1" dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
     <pivotHierarchy dragToData="1"/>
@@ -5299,7 +8347,7 @@
   <pivotTables>
     <pivotTable tabId="11" name="PivotTable7"/>
     <pivotTable tabId="11" name="PivotTable5"/>
-    <pivotTable tabId="11" name="PivotTable6"/>
+    <pivotTable tabId="11" name="PivotTable9"/>
   </pivotTables>
   <data>
     <olap pivotCacheId="21896247">
@@ -5327,7 +8375,7 @@
   <pivotTables>
     <pivotTable tabId="11" name="PivotTable7"/>
     <pivotTable tabId="11" name="PivotTable5"/>
-    <pivotTable tabId="11" name="PivotTable6"/>
+    <pivotTable tabId="11" name="PivotTable9"/>
   </pivotTables>
   <data>
     <olap pivotCacheId="21896247">
@@ -5344,7 +8392,57 @@
         </level>
       </levels>
       <selections count="1">
-        <selection n="[Range].[Geography].&amp;[Germany]"/>
+        <selection n="[Range].[Geography].[All]"/>
+      </selections>
+    </olap>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Age" xr10:uid="{2EED935B-3127-4638-A877-9031C7B9B574}" sourceName="[Range].[Age]">
+  <pivotTables>
+    <pivotTable tabId="11" name="PivotTable5"/>
+    <pivotTable tabId="11" name="PivotTable9"/>
+  </pivotTables>
+  <data>
+    <olap pivotCacheId="21896247">
+      <levels count="2">
+        <level uniqueName="[Range].[Age].[(All)]" sourceCaption="(All)" count="0"/>
+        <level uniqueName="[Range].[Age].[Age]" sourceCaption="Age" count="25">
+          <ranges>
+            <range startItem="0">
+              <i n="[Range].[Age].&amp;[24]" c="24"/>
+              <i n="[Range].[Age].&amp;[25]" c="25"/>
+              <i n="[Range].[Age].&amp;[27]" c="27"/>
+              <i n="[Range].[Age].&amp;[29]" c="29"/>
+              <i n="[Range].[Age].&amp;[31]" c="31"/>
+              <i n="[Range].[Age].&amp;[32]" c="32"/>
+              <i n="[Range].[Age].&amp;[33]" c="33"/>
+              <i n="[Range].[Age].&amp;[34]" c="34"/>
+              <i n="[Range].[Age].&amp;[35]" c="35"/>
+              <i n="[Range].[Age].&amp;[36]" c="36"/>
+              <i n="[Range].[Age].&amp;[37]" c="37"/>
+              <i n="[Range].[Age].&amp;[38]" c="38"/>
+              <i n="[Range].[Age].&amp;[39]" c="39"/>
+              <i n="[Range].[Age].&amp;[40]" c="40"/>
+              <i n="[Range].[Age].&amp;[41]" c="41"/>
+              <i n="[Range].[Age].&amp;[42]" c="42"/>
+              <i n="[Range].[Age].&amp;[43]" c="43"/>
+              <i n="[Range].[Age].&amp;[44]" c="44"/>
+              <i n="[Range].[Age].&amp;[45]" c="45"/>
+              <i n="[Range].[Age].&amp;[46]" c="46"/>
+              <i n="[Range].[Age].&amp;[49]" c="49"/>
+              <i n="[Range].[Age].&amp;[50]" c="50"/>
+              <i n="[Range].[Age].&amp;[51]" c="51"/>
+              <i n="[Range].[Age].&amp;[58]" c="58"/>
+              <i n="[Range].[Age].&amp;[61]" c="61"/>
+            </range>
+          </ranges>
+        </level>
+      </levels>
+      <selections count="1">
+        <selection n="[Range].[Age].[All]"/>
       </selections>
     </olap>
   </data>
@@ -5355,6 +8453,7 @@
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
   <slicer name="Gender" xr10:uid="{A7B22489-3F6F-43AC-AFB1-E15D3276F3A1}" cache="Slicer_Gender" caption="Gender" level="1" rowHeight="241300"/>
   <slicer name="Geography" xr10:uid="{09475EF3-8F17-4A70-8D18-2B86B3564AD5}" cache="Slicer_Geography" caption="Geography" level="1" rowHeight="241300"/>
+  <slicer name="Age" xr10:uid="{9E3666A0-AAF8-4F03-8243-78CA13E0F09D}" cache="Slicer_Age" caption="Age" startItem="1" level="1" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -5655,7 +8754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{405BBDA5-9549-47F1-A1C4-21A2FE50E670}">
-  <dimension ref="A3:G24"/>
+  <dimension ref="A3:G46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -5688,27 +8787,27 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B4" s="5">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="C4" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E4" s="4">
         <v>1</v>
       </c>
       <c r="F4" s="5">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="G4" s="5">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>70</v>
+        <v>26</v>
       </c>
       <c r="B5" s="5">
         <v>12</v>
@@ -5720,62 +8819,102 @@
         <v>2</v>
       </c>
       <c r="F5" s="5">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="G5" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5">
+        <v>16</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
       <c r="E6" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G6" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="E7" s="4" t="s">
+      <c r="A7" s="4" t="s">
         <v>70</v>
       </c>
+      <c r="B7" s="5">
+        <v>50</v>
+      </c>
+      <c r="C7" s="5">
+        <v>12</v>
+      </c>
+      <c r="E7" s="4">
+        <v>4</v>
+      </c>
       <c r="F7" s="5">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E8" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F8" s="5">
+        <v>50</v>
+      </c>
+      <c r="G8" s="5">
         <v>12</v>
       </c>
-      <c r="G7" s="5">
-        <v>4</v>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>71</v>
+      <c r="A12" s="4">
+        <v>24</v>
+      </c>
+      <c r="B12" s="5">
+        <v>3</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C13" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C14" s="5">
         <v>1</v>
@@ -5783,21 +8922,21 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B15" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15" s="5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B16" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" s="5">
         <v>0</v>
@@ -5805,10 +8944,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="B17" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C17" s="5">
         <v>0</v>
@@ -5816,7 +8955,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
@@ -5827,21 +8966,21 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
       </c>
       <c r="C19" s="5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B20" s="5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C20" s="5">
         <v>0</v>
@@ -5849,10 +8988,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="B21" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C21" s="5">
         <v>0</v>
@@ -5860,7 +8999,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -5871,33 +9010,242 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="B23" s="5">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="4">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5">
+        <v>3</v>
+      </c>
+      <c r="C24" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="4">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="4">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5">
+        <v>4</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="4">
+        <v>42</v>
+      </c>
+      <c r="B27" s="5">
+        <v>3</v>
+      </c>
+      <c r="C27" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="4">
+        <v>43</v>
+      </c>
+      <c r="B28" s="5">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="4">
+        <v>44</v>
+      </c>
+      <c r="B29" s="5">
+        <v>3</v>
+      </c>
+      <c r="C29" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="4">
+        <v>45</v>
+      </c>
+      <c r="B30" s="5">
+        <v>3</v>
+      </c>
+      <c r="C30" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="4">
+        <v>46</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="4">
+        <v>49</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="4">
+        <v>50</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="4">
+        <v>51</v>
+      </c>
+      <c r="B34" s="5">
+        <v>1</v>
+      </c>
+      <c r="C34" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="4">
+        <v>58</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="4">
+        <v>61</v>
+      </c>
+      <c r="B36" s="5">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B37" s="5">
+        <v>50</v>
+      </c>
+      <c r="C37" s="5">
         <v>12</v>
       </c>
-      <c r="C24" s="5">
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
+        <v>72</v>
+      </c>
+      <c r="C41" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B42" s="5">
+        <v>15</v>
+      </c>
+      <c r="C42" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B43" s="5">
+        <v>22</v>
+      </c>
+      <c r="C43" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="5">
+        <v>10</v>
+      </c>
+      <c r="C44" s="5">
         <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" s="5">
+        <v>3</v>
+      </c>
+      <c r="C45" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="B46" s="5">
+        <v>50</v>
+      </c>
+      <c r="C46" s="5">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
       <x14:slicerList>
-        <x14:slicer r:id="rId5"/>
+        <x14:slicer r:id="rId6"/>
       </x14:slicerList>
     </ext>
   </extLst>
